--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#19</t>
+    <t>#20</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 07:10:14 UTC</t>
+    <t>2026-06-22 07:49:44 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -144,7 +144,7 @@
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, .sidebar)
-Wait timed out after 20069ms</t>
+Wait timed out after 20007ms</t>
   </si>
   <si>
     <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
@@ -160,7 +160,7 @@
   </si>
   <si>
     <t xml:space="preserve">Waiting for element to be located By(css selector, .sidebar)
-Wait timed out after 20108ms</t>
+Wait timed out after 20097ms</t>
   </si>
   <si>
     <t>TC-001 App Launch</t>
@@ -961,7 +961,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>698</v>
+        <v>1022</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -975,7 +975,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>751</v>
+        <v>1156</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -989,7 +989,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>2374</v>
+        <v>2884</v>
       </c>
       <c r="D4" t="s">
         <v>37</v>
@@ -1003,7 +1003,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>1187</v>
+        <v>860</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1017,7 +1017,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>1210</v>
+        <v>1230</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1031,7 +1031,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>1758</v>
+        <v>1488</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1045,7 +1045,7 @@
         <v>36</v>
       </c>
       <c r="C8">
-        <v>21672</v>
+        <v>21342</v>
       </c>
       <c r="D8" t="s">
         <v>42</v>
@@ -1059,7 +1059,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2431</v>
+        <v>2410</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1073,7 +1073,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1087,7 +1087,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1101,7 +1101,7 @@
         <v>36</v>
       </c>
       <c r="C12">
-        <v>21035</v>
+        <v>21356</v>
       </c>
       <c r="D12" t="s">
         <v>47</v>
@@ -1146,7 +1146,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5475</v>
+        <v>5235</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1160,7 +1160,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7662</v>
+        <v>7859</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1174,7 +1174,7 @@
         <v>36</v>
       </c>
       <c r="C4">
-        <v>19668</v>
+        <v>19354</v>
       </c>
       <c r="D4" t="s">
         <v>37</v>
@@ -1188,7 +1188,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>44979</v>
+        <v>43010</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1202,7 +1202,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14404</v>
+        <v>14377</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1216,7 +1216,7 @@
         <v>36</v>
       </c>
       <c r="C7">
-        <v>17358</v>
+        <v>17323</v>
       </c>
       <c r="D7" t="s">
         <v>54</v>
@@ -1230,7 +1230,7 @@
         <v>36</v>
       </c>
       <c r="C8">
-        <v>76819</v>
+        <v>77828</v>
       </c>
       <c r="D8" t="s">
         <v>56</v>
@@ -1244,7 +1244,7 @@
         <v>36</v>
       </c>
       <c r="C9">
-        <v>20113</v>
+        <v>20145</v>
       </c>
       <c r="D9" t="s">
         <v>56</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#20</t>
+    <t>#21</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 07:49:44 UTC</t>
+    <t>2026-06-22 08:53:59 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -62,18 +62,21 @@
     <t>🌐 Web Application E2E</t>
   </si>
   <si>
-    <t>96.7%</t>
+    <t>100.0%</t>
+  </si>
+  <si>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>📱 Android Mobile E2E</t>
+  </si>
+  <si>
+    <t>98.7%</t>
   </si>
   <si>
     <t>FAIL</t>
   </si>
   <si>
-    <t>📱 Android Mobile E2E</t>
-  </si>
-  <si>
-    <t>98.7%</t>
-  </si>
-  <si>
     <t>🛡️ Backend Security Scan</t>
   </si>
   <si>
@@ -89,9 +92,6 @@
     <t>🔒 Security E2E Tests</t>
   </si>
   <si>
-    <t>66.7%</t>
-  </si>
-  <si>
     <t>📈 Performance Load Test</t>
   </si>
   <si>
@@ -125,53 +125,45 @@
     <t>should login with valid credentials and reach the dashboard</t>
   </si>
   <si>
+    <t>should reject invalid credentials with an error message</t>
+  </si>
+  <si>
+    <t>should open the sign-up form from landing</t>
+  </si>
+  <si>
+    <t>Security — should reject login for invalid credentials</t>
+  </si>
+  <si>
+    <t>Security — should enforce session termination and clean storage upon logout</t>
+  </si>
+  <si>
+    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
+  </si>
+  <si>
+    <t>Security — should block unauthorized database write attempts to restricted user paths</t>
+  </si>
+  <si>
+    <t>Security — should block unauthorized database read attempts to restricted user profiles</t>
+  </si>
+  <si>
+    <t>Security — should securely sanitize and encode XSS script payloads in text fields</t>
+  </si>
+  <si>
+    <t>TC-001 App Launch</t>
+  </si>
+  <si>
+    <t>TC-002 Login Screen</t>
+  </si>
+  <si>
+    <t>TC-003 Valid Login</t>
+  </si>
+  <si>
     <t>failed</t>
   </si>
   <si>
     <t>Test account is not email verified.</t>
   </si>
   <si>
-    <t>should reject invalid credentials with an error message</t>
-  </si>
-  <si>
-    <t>should open the sign-up form from landing</t>
-  </si>
-  <si>
-    <t>Security — should reject login for invalid credentials</t>
-  </si>
-  <si>
-    <t>Security — should enforce session termination and clean storage upon logout</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, .sidebar)
-Wait timed out after 20007ms</t>
-  </si>
-  <si>
-    <t>Security — should prevent access to protected routes/dashboard for unauthenticated users</t>
-  </si>
-  <si>
-    <t>Security — should block unauthorized database write attempts to restricted user paths</t>
-  </si>
-  <si>
-    <t>Security — should block unauthorized database read attempts to restricted user profiles</t>
-  </si>
-  <si>
-    <t>Security — should securely sanitize and encode XSS script payloads in text fields</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Waiting for element to be located By(css selector, .sidebar)
-Wait timed out after 20097ms</t>
-  </si>
-  <si>
-    <t>TC-001 App Launch</t>
-  </si>
-  <si>
-    <t>TC-002 Login Screen</t>
-  </si>
-  <si>
-    <t>TC-003 Valid Login</t>
-  </si>
-  <si>
     <t>TC-004 Invalid Credentials</t>
   </si>
   <si>
@@ -248,9 +240,6 @@
   </si>
   <si>
     <t>Failed Controls</t>
-  </si>
-  <si>
-    <t>VULNERABLE</t>
   </si>
   <si>
     <t>Metric Name</t>
@@ -334,11 +323,11 @@
     </font>
     <font>
       <b/>
-      <color rgb="B91C1C"/>
+      <color rgb="047857"/>
     </font>
     <font>
       <b/>
-      <color rgb="047857"/>
+      <color rgb="B91C1C"/>
     </font>
   </fonts>
   <fills count="6">
@@ -360,12 +349,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
+        <fgColor rgb="D1FAE5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="D1FAE5"/>
+        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -812,10 +801,10 @@
         <v>300</v>
       </c>
       <c r="C8">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="D8">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>0</v>
@@ -846,51 +835,51 @@
       <c r="F9" t="s">
         <v>18</v>
       </c>
-      <c r="G9" s="5" t="s">
-        <v>16</v>
+      <c r="G9" s="6" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
       <c r="C10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F10" t="s">
-        <v>21</v>
-      </c>
-      <c r="G10" s="6" t="s">
         <v>22</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B11">
         <v>6</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D11">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E11">
         <v>0</v>
       </c>
       <c r="F11" t="s">
-        <v>24</v>
+        <v>15</v>
       </c>
       <c r="G11" s="5" t="s">
         <v>16</v>
@@ -904,18 +893,18 @@
         <v>5824</v>
       </c>
       <c r="C12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E12" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="F12" t="s">
         <v>26</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="5" t="s">
         <v>27</v>
       </c>
     </row>
@@ -935,8 +924,7 @@
   <cols>
     <col min="1" max="1" width="91" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="92" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -961,7 +949,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>1022</v>
+        <v>994</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -975,7 +963,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>1156</v>
+        <v>816</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -986,24 +974,24 @@
         <v>35</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>2884</v>
+        <v>2793</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5">
-        <v>860</v>
+        <v>1508</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1011,13 +999,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6">
-        <v>1230</v>
+        <v>1135</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1025,13 +1013,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B7" t="s">
         <v>32</v>
       </c>
       <c r="C7">
-        <v>1488</v>
+        <v>2107</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1039,27 +1027,27 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>21342</v>
+        <v>7097</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B9" t="s">
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2410</v>
+        <v>2834</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1067,13 +1055,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10">
-        <v>565</v>
+        <v>750</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1081,13 +1069,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11">
-        <v>174</v>
+        <v>237</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1095,16 +1083,16 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="B12" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C12">
-        <v>21356</v>
+        <v>9071</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1140,13 +1128,13 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B2" t="s">
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5235</v>
+        <v>5301</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1154,13 +1142,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B3" t="s">
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7859</v>
+        <v>7693</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1168,27 +1156,27 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C4">
-        <v>19354</v>
+        <v>18722</v>
       </c>
       <c r="D4" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5">
-        <v>43010</v>
+        <v>38656</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1196,13 +1184,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14377</v>
+        <v>14318</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1210,44 +1198,44 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B7" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C7">
-        <v>17323</v>
+        <v>17331</v>
       </c>
       <c r="D7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C8">
-        <v>77828</v>
+        <v>76254</v>
       </c>
       <c r="D8" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B9" t="s">
-        <v>36</v>
+        <v>47</v>
       </c>
       <c r="C9">
-        <v>20145</v>
+        <v>20134</v>
       </c>
       <c r="D9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
   </sheetData>
@@ -1269,13 +1257,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>58</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>60</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>13</v>
@@ -1283,94 +1271,94 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B3" t="s">
         <v>61</v>
-      </c>
-      <c r="B3" t="s">
-        <v>63</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" t="s">
         <v>69</v>
       </c>
-      <c r="B6" t="s">
-        <v>70</v>
-      </c>
-      <c r="C6" t="s">
-        <v>71</v>
-      </c>
       <c r="D6" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>70</v>
+      </c>
+      <c r="C7" t="s">
         <v>69</v>
       </c>
-      <c r="B7" t="s">
-        <v>72</v>
-      </c>
-      <c r="C7" t="s">
-        <v>71</v>
-      </c>
       <c r="D7" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1381,13 +1369,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>71</v>
+      </c>
+      <c r="B9" t="s">
         <v>73</v>
       </c>
-      <c r="B9" t="s">
-        <v>75</v>
-      </c>
       <c r="C9">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1395,16 +1383,16 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>77</v>
+        <v>23</v>
       </c>
     </row>
   </sheetData>
@@ -1425,43 +1413,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B3" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="C3" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -1469,46 +1457,46 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="C5" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B6" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B7" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#21</t>
+    <t>#22</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 08:53:59 UTC</t>
+    <t>2026-06-22 09:38:28 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -949,7 +949,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>994</v>
+        <v>797</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -963,7 +963,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>816</v>
+        <v>1103</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -977,7 +977,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>2793</v>
+        <v>3414</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -991,7 +991,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>1508</v>
+        <v>918</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1005,7 +1005,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>1135</v>
+        <v>736</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1019,7 +1019,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>2107</v>
+        <v>1986</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1033,7 +1033,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>7097</v>
+        <v>7354</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1047,7 +1047,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2834</v>
+        <v>3051</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>750</v>
+        <v>793</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1075,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>237</v>
+        <v>255</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1089,7 +1089,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>9071</v>
+        <v>9291</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1134,7 +1134,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5301</v>
+        <v>5260</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1148,7 +1148,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7693</v>
+        <v>7820</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1162,7 +1162,7 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>18722</v>
+        <v>18330</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
@@ -1176,7 +1176,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>38656</v>
+        <v>36690</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1190,7 +1190,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14318</v>
+        <v>14341</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1204,7 +1204,7 @@
         <v>47</v>
       </c>
       <c r="C7">
-        <v>17331</v>
+        <v>17338</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
@@ -1218,7 +1218,7 @@
         <v>47</v>
       </c>
       <c r="C8">
-        <v>76254</v>
+        <v>76191</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -1232,7 +1232,7 @@
         <v>47</v>
       </c>
       <c r="C9">
-        <v>20134</v>
+        <v>20111</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#22</t>
+    <t>#23</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 09:38:28 UTC</t>
+    <t>2026-06-22 10:32:15 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -949,7 +949,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>797</v>
+        <v>329</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -963,7 +963,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>1103</v>
+        <v>877</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -977,7 +977,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>3414</v>
+        <v>2483</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -991,7 +991,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>918</v>
+        <v>1012</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1005,7 +1005,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>736</v>
+        <v>845</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1019,7 +1019,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>1986</v>
+        <v>976</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1033,7 +1033,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>7354</v>
+        <v>6486</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1047,7 +1047,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>3051</v>
+        <v>2777</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1061,7 +1061,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>793</v>
+        <v>723</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1075,7 +1075,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1089,7 +1089,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>9291</v>
+        <v>8910</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1134,7 +1134,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5260</v>
+        <v>5300</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1148,7 +1148,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7820</v>
+        <v>7815</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1162,7 +1162,7 @@
         <v>47</v>
       </c>
       <c r="C4">
-        <v>18330</v>
+        <v>18201</v>
       </c>
       <c r="D4" t="s">
         <v>48</v>
@@ -1176,7 +1176,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>36690</v>
+        <v>37830</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1190,7 +1190,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14341</v>
+        <v>14329</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1204,7 +1204,7 @@
         <v>47</v>
       </c>
       <c r="C7">
-        <v>17338</v>
+        <v>17304</v>
       </c>
       <c r="D7" t="s">
         <v>52</v>
@@ -1218,7 +1218,7 @@
         <v>47</v>
       </c>
       <c r="C8">
-        <v>76191</v>
+        <v>76275</v>
       </c>
       <c r="D8" t="s">
         <v>54</v>
@@ -1232,7 +1232,7 @@
         <v>47</v>
       </c>
       <c r="C9">
-        <v>20111</v>
+        <v>20106</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="155" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#23</t>
+    <t>#24</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 10:32:15 UTC</t>
+    <t>2026-06-22 12:18:51 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -71,7 +71,7 @@
     <t>📱 Android Mobile E2E</t>
   </si>
   <si>
-    <t>98.7%</t>
+    <t>99.3%</t>
   </si>
   <si>
     <t>FAIL</t>
@@ -158,31 +158,40 @@
     <t>TC-003 Valid Login</t>
   </si>
   <si>
+    <t>TC-004 Invalid Credentials</t>
+  </si>
+  <si>
+    <t>TC-005 Empty Form Validation</t>
+  </si>
+  <si>
+    <t>TC-006 Navigate to Sign Up</t>
+  </si>
+  <si>
     <t>failed</t>
   </si>
   <si>
-    <t>Test account is not email verified.</t>
-  </si>
-  <si>
-    <t>TC-004 Invalid Credentials</t>
-  </si>
-  <si>
-    <t>TC-005 Empty Form Validation</t>
-  </si>
-  <si>
-    <t>TC-006 Navigate to Sign Up</t>
-  </si>
-  <si>
-    <t>Can't call click on element with selector "//android.widget.Button[@text="Sign Up"]" because element wasn't found</t>
+    <t>Can't call click on element with selector "//android.view.ViewGroup[@content-desc="signup-button"] | //android.widget.TextView[@text="Sign Up" or @text="SIGN UP"]" because element wasn't found</t>
   </si>
   <si>
     <t>TC-007 Dashboard Tabs</t>
   </si>
   <si>
+    <t>TC-008 Logout</t>
+  </si>
+  <si>
     <t>element ("~avatar-button") still not existing after 20000ms</t>
   </si>
   <si>
-    <t>TC-008 Logout</t>
+    <t>TC-009 Lost Tab</t>
+  </si>
+  <si>
+    <t>TC-010 Found Tab</t>
+  </si>
+  <si>
+    <t>TC-011 Search Tab</t>
+  </si>
+  <si>
+    <t>TC-012 Chat Tab</t>
   </si>
   <si>
     <t>Security Scope</t>
@@ -824,10 +833,10 @@
         <v>300</v>
       </c>
       <c r="C9">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="D9">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -949,7 +958,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>329</v>
+        <v>976</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -963,7 +972,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>877</v>
+        <v>766</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -977,7 +986,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>2483</v>
+        <v>2653</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -991,7 +1000,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>1012</v>
+        <v>1694</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1005,7 +1014,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>845</v>
+        <v>1346</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1019,7 +1028,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>976</v>
+        <v>1877</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1033,7 +1042,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>6486</v>
+        <v>6882</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1047,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2777</v>
+        <v>2633</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1061,7 +1070,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>723</v>
+        <v>744</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1075,7 +1084,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1089,7 +1098,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>8910</v>
+        <v>8698</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1103,13 +1112,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="116" customWidth="1"/>
+    <col min="4" max="4" width="195" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1134,7 +1143,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5300</v>
+        <v>5325</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1148,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7815</v>
+        <v>7745</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1159,24 +1168,24 @@
         <v>46</v>
       </c>
       <c r="B4" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C4">
-        <v>18201</v>
+        <v>19145</v>
       </c>
       <c r="D4" t="s">
-        <v>48</v>
+        <v>33</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B5" t="s">
         <v>32</v>
       </c>
       <c r="C5">
-        <v>37830</v>
+        <v>54266</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1184,13 +1193,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B6" t="s">
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14329</v>
+        <v>14339</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1198,44 +1207,100 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>49</v>
+      </c>
+      <c r="B7" t="s">
+        <v>50</v>
+      </c>
+      <c r="C7">
+        <v>17334</v>
+      </c>
+      <c r="D7" t="s">
         <v>51</v>
-      </c>
-      <c r="B7" t="s">
-        <v>47</v>
-      </c>
-      <c r="C7">
-        <v>17304</v>
-      </c>
-      <c r="D7" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>47</v>
+        <v>32</v>
       </c>
       <c r="C8">
-        <v>76275</v>
+        <v>37698</v>
       </c>
       <c r="D8" t="s">
-        <v>54</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B9" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="C9">
-        <v>20106</v>
+        <v>20764</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>55</v>
+      </c>
+      <c r="B10" t="s">
+        <v>32</v>
+      </c>
+      <c r="C10">
+        <v>2884</v>
+      </c>
+      <c r="D10" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>56</v>
+      </c>
+      <c r="B11" t="s">
+        <v>32</v>
+      </c>
+      <c r="C11">
+        <v>2763</v>
+      </c>
+      <c r="D11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>57</v>
+      </c>
+      <c r="B12" t="s">
+        <v>32</v>
+      </c>
+      <c r="C12">
+        <v>2251</v>
+      </c>
+      <c r="D12" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>58</v>
+      </c>
+      <c r="B13" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13">
+        <v>2271</v>
+      </c>
+      <c r="D13" t="s">
+        <v>33</v>
       </c>
     </row>
   </sheetData>
@@ -1257,13 +1322,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>13</v>
@@ -1271,10 +1336,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1285,55 +1350,55 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B3" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B4" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="B5" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B6" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -1341,13 +1406,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1355,10 +1420,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B8" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1369,10 +1434,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B9" t="s">
-        <v>73</v>
+        <v>76</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1383,10 +1448,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="B10" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1413,43 +1478,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="B3" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="C3" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B4" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -1457,46 +1522,46 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C6" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#24</t>
+    <t>#25</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 12:18:51 UTC</t>
+    <t>2026-06-22 12:52:48 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -170,7 +170,7 @@
     <t>failed</t>
   </si>
   <si>
-    <t>Can't call click on element with selector "//android.view.ViewGroup[@content-desc="signup-button"] | //android.widget.TextView[@text="Sign Up" or @text="SIGN UP"]" because element wasn't found</t>
+    <t>element ("//android.widget.EditText[@hint="Email"]") still not existing after 10000ms</t>
   </si>
   <si>
     <t>TC-007 Dashboard Tabs</t>
@@ -179,7 +179,7 @@
     <t>TC-008 Logout</t>
   </si>
   <si>
-    <t>element ("~avatar-button") still not existing after 20000ms</t>
+    <t>org.eclipse.wst.xml.xpath2.processor.XPathParserException: JFlex lexer error: Unknown character at line 1 col 32: ~</t>
   </si>
   <si>
     <t>TC-009 Lost Tab</t>
@@ -958,7 +958,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>976</v>
+        <v>691</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -972,7 +972,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>766</v>
+        <v>1392</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -986,7 +986,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>2653</v>
+        <v>2993</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -1000,7 +1000,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>1694</v>
+        <v>1125</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1014,7 +1014,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>1346</v>
+        <v>1007</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1028,7 +1028,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>1877</v>
+        <v>1571</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1042,7 +1042,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>6882</v>
+        <v>6910</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1056,7 +1056,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2633</v>
+        <v>2757</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1070,7 +1070,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>744</v>
+        <v>598</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1084,7 +1084,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1098,7 +1098,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>8698</v>
+        <v>8943</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1118,7 +1118,7 @@
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="195" customWidth="1"/>
+    <col min="4" max="4" width="118" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -1143,7 +1143,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5325</v>
+        <v>5377</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1157,7 +1157,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>7745</v>
+        <v>8412</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1171,7 +1171,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>19145</v>
+        <v>19924</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -1185,7 +1185,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>54266</v>
+        <v>41136</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1199,7 +1199,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14339</v>
+        <v>14343</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1213,7 +1213,7 @@
         <v>50</v>
       </c>
       <c r="C7">
-        <v>17334</v>
+        <v>26868</v>
       </c>
       <c r="D7" t="s">
         <v>51</v>
@@ -1227,7 +1227,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>37698</v>
+        <v>52472</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1241,7 +1241,7 @@
         <v>50</v>
       </c>
       <c r="C9">
-        <v>20764</v>
+        <v>850</v>
       </c>
       <c r="D9" t="s">
         <v>54</v>
@@ -1255,7 +1255,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>2884</v>
+        <v>2857</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1269,7 +1269,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>2763</v>
+        <v>2749</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1283,7 +1283,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>2251</v>
+        <v>2230</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1297,7 +1297,7 @@
         <v>32</v>
       </c>
       <c r="C13">
-        <v>2271</v>
+        <v>2257</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="95">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#25</t>
+    <t>#26</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 12:52:48 UTC</t>
+    <t>2026-06-22 13:21:52 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -71,7 +71,7 @@
     <t>📱 Android Mobile E2E</t>
   </si>
   <si>
-    <t>99.3%</t>
+    <t>99.7%</t>
   </si>
   <si>
     <t>FAIL</t>
@@ -167,19 +167,16 @@
     <t>TC-006 Navigate to Sign Up</t>
   </si>
   <si>
+    <t>TC-007 Dashboard Tabs</t>
+  </si>
+  <si>
+    <t>TC-008 Logout</t>
+  </si>
+  <si>
     <t>failed</t>
   </si>
   <si>
-    <t>element ("//android.widget.EditText[@hint="Email"]") still not existing after 10000ms</t>
-  </si>
-  <si>
-    <t>TC-007 Dashboard Tabs</t>
-  </si>
-  <si>
-    <t>TC-008 Logout</t>
-  </si>
-  <si>
-    <t>org.eclipse.wst.xml.xpath2.processor.XPathParserException: JFlex lexer error: Unknown character at line 1 col 32: ~</t>
+    <t>element ("//*[@resource-id="logout-button"] | //*[@content-desc="logout-button"]") still not existing after 20000ms</t>
   </si>
   <si>
     <t>TC-009 Lost Tab</t>
@@ -833,10 +830,10 @@
         <v>300</v>
       </c>
       <c r="C9">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="D9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E9">
         <v>0</v>
@@ -958,7 +955,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>691</v>
+        <v>1005</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -972,7 +969,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>1392</v>
+        <v>805</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -986,7 +983,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>2993</v>
+        <v>3225</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -1000,7 +997,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>1125</v>
+        <v>868</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1014,7 +1011,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>1007</v>
+        <v>1120</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1028,7 +1025,7 @@
         <v>32</v>
       </c>
       <c r="C7">
-        <v>1571</v>
+        <v>1213</v>
       </c>
       <c r="D7" t="s">
         <v>33</v>
@@ -1042,7 +1039,7 @@
         <v>32</v>
       </c>
       <c r="C8">
-        <v>6910</v>
+        <v>6932</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1056,7 +1053,7 @@
         <v>32</v>
       </c>
       <c r="C9">
-        <v>2757</v>
+        <v>2446</v>
       </c>
       <c r="D9" t="s">
         <v>33</v>
@@ -1070,7 +1067,7 @@
         <v>32</v>
       </c>
       <c r="C10">
-        <v>598</v>
+        <v>583</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1084,7 +1081,7 @@
         <v>32</v>
       </c>
       <c r="C11">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1098,7 +1095,7 @@
         <v>32</v>
       </c>
       <c r="C12">
-        <v>8943</v>
+        <v>8519</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1143,7 +1140,7 @@
         <v>32</v>
       </c>
       <c r="C2">
-        <v>5377</v>
+        <v>5336</v>
       </c>
       <c r="D2" t="s">
         <v>33</v>
@@ -1157,7 +1154,7 @@
         <v>32</v>
       </c>
       <c r="C3">
-        <v>8412</v>
+        <v>7742</v>
       </c>
       <c r="D3" t="s">
         <v>33</v>
@@ -1171,7 +1168,7 @@
         <v>32</v>
       </c>
       <c r="C4">
-        <v>19924</v>
+        <v>19522</v>
       </c>
       <c r="D4" t="s">
         <v>33</v>
@@ -1185,7 +1182,7 @@
         <v>32</v>
       </c>
       <c r="C5">
-        <v>41136</v>
+        <v>48967</v>
       </c>
       <c r="D5" t="s">
         <v>33</v>
@@ -1199,7 +1196,7 @@
         <v>32</v>
       </c>
       <c r="C6">
-        <v>14343</v>
+        <v>14367</v>
       </c>
       <c r="D6" t="s">
         <v>33</v>
@@ -1210,24 +1207,24 @@
         <v>49</v>
       </c>
       <c r="B7" t="s">
-        <v>50</v>
+        <v>32</v>
       </c>
       <c r="C7">
-        <v>26868</v>
+        <v>17013</v>
       </c>
       <c r="D7" t="s">
-        <v>51</v>
+        <v>33</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B8" t="s">
         <v>32</v>
       </c>
       <c r="C8">
-        <v>52472</v>
+        <v>52940</v>
       </c>
       <c r="D8" t="s">
         <v>33</v>
@@ -1235,27 +1232,27 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>51</v>
+      </c>
+      <c r="B9" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9">
+        <v>24607</v>
+      </c>
+      <c r="D9" t="s">
         <v>53</v>
-      </c>
-      <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="C9">
-        <v>850</v>
-      </c>
-      <c r="D9" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="B10" t="s">
         <v>32</v>
       </c>
       <c r="C10">
-        <v>2857</v>
+        <v>2918</v>
       </c>
       <c r="D10" t="s">
         <v>33</v>
@@ -1263,13 +1260,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="B11" t="s">
         <v>32</v>
       </c>
       <c r="C11">
-        <v>2749</v>
+        <v>2780</v>
       </c>
       <c r="D11" t="s">
         <v>33</v>
@@ -1277,13 +1274,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>32</v>
       </c>
       <c r="C12">
-        <v>2230</v>
+        <v>2268</v>
       </c>
       <c r="D12" t="s">
         <v>33</v>
@@ -1291,13 +1288,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B13" t="s">
         <v>32</v>
       </c>
       <c r="C13">
-        <v>2257</v>
+        <v>2313</v>
       </c>
       <c r="D13" t="s">
         <v>33</v>
@@ -1322,13 +1319,13 @@
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>59</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="C1" s="7" t="s">
         <v>60</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>61</v>
       </c>
       <c r="D1" s="7" t="s">
         <v>13</v>
@@ -1336,10 +1333,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" t="s">
         <v>62</v>
-      </c>
-      <c r="B2" t="s">
-        <v>63</v>
       </c>
       <c r="C2">
         <v>0</v>
@@ -1350,55 +1347,55 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B4" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="B5" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>69</v>
+      </c>
+      <c r="B6" t="s">
         <v>70</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>71</v>
-      </c>
-      <c r="C6" t="s">
-        <v>72</v>
       </c>
       <c r="D6" t="s">
         <v>23</v>
@@ -1406,13 +1403,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="B7" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="C7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D7" t="s">
         <v>23</v>
@@ -1420,10 +1417,10 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>73</v>
+      </c>
+      <c r="B8" t="s">
         <v>74</v>
-      </c>
-      <c r="B8" t="s">
-        <v>75</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1434,10 +1431,10 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B9" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -1448,10 +1445,10 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="B10" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="C10">
         <v>0</v>
@@ -1478,43 +1475,43 @@
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>60</v>
+      </c>
+      <c r="C1" s="7" t="s">
         <v>78</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>79</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B3" t="s">
         <v>82</v>
       </c>
-      <c r="B3" t="s">
+      <c r="C3" t="s">
         <v>83</v>
-      </c>
-      <c r="C3" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>84</v>
+      </c>
+      <c r="B4" t="s">
         <v>85</v>
-      </c>
-      <c r="B4" t="s">
-        <v>86</v>
       </c>
       <c r="C4" t="s">
         <v>33</v>
@@ -1522,46 +1519,46 @@
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>86</v>
+      </c>
+      <c r="B5" t="s">
         <v>87</v>
       </c>
-      <c r="B5" t="s">
+      <c r="C5" t="s">
         <v>88</v>
-      </c>
-      <c r="C5" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" t="s">
         <v>90</v>
       </c>
-      <c r="B6" t="s">
-        <v>91</v>
-      </c>
       <c r="C6" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>91</v>
+      </c>
+      <c r="B7" t="s">
         <v>92</v>
       </c>
-      <c r="B7" t="s">
-        <v>93</v>
-      </c>
       <c r="C7" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="91">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#26</t>
+    <t>#27</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 13:21:52 UTC</t>
+    <t>2026-06-22 14:04:41 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -71,12 +71,6 @@
     <t>📱 Android Mobile E2E</t>
   </si>
   <si>
-    <t>99.7%</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
     <t>🛡️ Backend Security Scan</t>
   </si>
   <si>
@@ -171,12 +165,6 @@
   </si>
   <si>
     <t>TC-008 Logout</t>
-  </si>
-  <si>
-    <t>failed</t>
-  </si>
-  <si>
-    <t>element ("//*[@resource-id="logout-button"] | //*[@content-desc="logout-button"]") still not existing after 20000ms</t>
   </si>
   <si>
     <t>TC-009 Lost Tab</t>
@@ -306,7 +294,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -331,12 +319,8 @@
       <b/>
       <color rgb="047857"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="B91C1C"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -356,11 +340,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -383,7 +362,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -392,7 +371,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -830,47 +808,47 @@
         <v>300</v>
       </c>
       <c r="C9">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="D9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E9">
         <v>0</v>
       </c>
       <c r="F9" t="s">
-        <v>18</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>19</v>
+        <v>15</v>
+      </c>
+      <c r="G9" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B10">
         <v>300</v>
       </c>
       <c r="C10" t="s">
+        <v>19</v>
+      </c>
+      <c r="D10" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" t="s">
+        <v>19</v>
+      </c>
+      <c r="F10" t="s">
+        <v>20</v>
+      </c>
+      <c r="G10" s="5" t="s">
         <v>21</v>
-      </c>
-      <c r="D10" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>23</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -893,25 +871,25 @@
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>5824</v>
       </c>
       <c r="C12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="E12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="F12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G12" s="5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -934,171 +912,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>1005</v>
+        <v>1024</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>805</v>
+        <v>1562</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>3225</v>
+        <v>3551</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>868</v>
+        <v>928</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>1120</v>
+        <v>1105</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>6932</v>
+        <v>6910</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>2446</v>
+        <v>3046</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>583</v>
+        <v>717</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>176</v>
+        <v>226</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>8519</v>
+        <v>8475</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1114,190 +1092,189 @@
   <cols>
     <col min="1" max="1" width="31" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
-    <col min="4" max="4" width="118" customWidth="1"/>
+    <col min="3" max="4" width="16" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>26</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>28</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C2">
-        <v>5336</v>
+        <v>5270</v>
       </c>
       <c r="D2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C3">
-        <v>7742</v>
+        <v>7773</v>
       </c>
       <c r="D3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B4" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C4">
-        <v>19522</v>
+        <v>19919</v>
       </c>
       <c r="D4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B5" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C5">
-        <v>48967</v>
+        <v>31555</v>
       </c>
       <c r="D5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C6">
-        <v>14367</v>
+        <v>14332</v>
       </c>
       <c r="D6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7">
-        <v>17013</v>
+        <v>16528</v>
       </c>
       <c r="D7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B8" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C8">
-        <v>52940</v>
+        <v>51990</v>
       </c>
       <c r="D8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B9" t="s">
-        <v>52</v>
+        <v>30</v>
       </c>
       <c r="C9">
-        <v>24607</v>
+        <v>20967</v>
       </c>
       <c r="D9" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10">
-        <v>2918</v>
+        <v>2991</v>
       </c>
       <c r="D10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C11">
-        <v>2780</v>
+        <v>2799</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="B12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C12">
-        <v>2268</v>
+        <v>2232</v>
       </c>
       <c r="D12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="B13" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C13">
-        <v>2313</v>
+        <v>2223</v>
       </c>
       <c r="D13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
   </sheetData>
@@ -1318,109 +1295,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B2" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B3" t="s">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>57</v>
+      </c>
+      <c r="B4" t="s">
         <v>61</v>
-      </c>
-      <c r="B4" t="s">
-        <v>65</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>61</v>
+        <v>57</v>
       </c>
       <c r="B5" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D6" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="D7" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B8" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1431,30 +1408,30 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B9" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C9">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="B10" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
   </sheetData>
@@ -1474,91 +1451,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>78</v>
+      <c r="A1" s="6" t="s">
+        <v>73</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>74</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="B3" t="s">
-        <v>82</v>
+        <v>78</v>
       </c>
       <c r="C3" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="B4" t="s">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="C4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>86</v>
+        <v>82</v>
       </c>
       <c r="B5" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="C5" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="B6" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="C6" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B7" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C7" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#27</t>
+    <t>#28</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 14:04:41 UTC</t>
+    <t>2026-06-22 14:40:16 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -933,7 +933,7 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>1024</v>
+        <v>508</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
@@ -947,7 +947,7 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>1562</v>
+        <v>1177</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
@@ -961,7 +961,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>3551</v>
+        <v>3249</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -975,7 +975,7 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>928</v>
+        <v>985</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -989,7 +989,7 @@
         <v>30</v>
       </c>
       <c r="C6">
-        <v>1105</v>
+        <v>941</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -1003,7 +1003,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>1215</v>
+        <v>1819</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -1017,7 +1017,7 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>6910</v>
+        <v>7341</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -1031,7 +1031,7 @@
         <v>30</v>
       </c>
       <c r="C9">
-        <v>3046</v>
+        <v>2498</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1045,7 +1045,7 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>717</v>
+        <v>554</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -1059,7 +1059,7 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>226</v>
+        <v>173</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
@@ -1073,7 +1073,7 @@
         <v>30</v>
       </c>
       <c r="C12">
-        <v>8475</v>
+        <v>9506</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -1117,7 +1117,7 @@
         <v>30</v>
       </c>
       <c r="C2">
-        <v>5270</v>
+        <v>5218</v>
       </c>
       <c r="D2" t="s">
         <v>31</v>
@@ -1131,7 +1131,7 @@
         <v>30</v>
       </c>
       <c r="C3">
-        <v>7773</v>
+        <v>7815</v>
       </c>
       <c r="D3" t="s">
         <v>31</v>
@@ -1145,7 +1145,7 @@
         <v>30</v>
       </c>
       <c r="C4">
-        <v>19919</v>
+        <v>18802</v>
       </c>
       <c r="D4" t="s">
         <v>31</v>
@@ -1159,7 +1159,7 @@
         <v>30</v>
       </c>
       <c r="C5">
-        <v>31555</v>
+        <v>31011</v>
       </c>
       <c r="D5" t="s">
         <v>31</v>
@@ -1173,7 +1173,7 @@
         <v>30</v>
       </c>
       <c r="C6">
-        <v>14332</v>
+        <v>14331</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -1187,7 +1187,7 @@
         <v>30</v>
       </c>
       <c r="C7">
-        <v>16528</v>
+        <v>16471</v>
       </c>
       <c r="D7" t="s">
         <v>31</v>
@@ -1201,7 +1201,7 @@
         <v>30</v>
       </c>
       <c r="C8">
-        <v>51990</v>
+        <v>52148</v>
       </c>
       <c r="D8" t="s">
         <v>31</v>
@@ -1215,7 +1215,7 @@
         <v>30</v>
       </c>
       <c r="C9">
-        <v>20967</v>
+        <v>21398</v>
       </c>
       <c r="D9" t="s">
         <v>31</v>
@@ -1229,7 +1229,7 @@
         <v>30</v>
       </c>
       <c r="C10">
-        <v>2991</v>
+        <v>3047</v>
       </c>
       <c r="D10" t="s">
         <v>31</v>
@@ -1243,7 +1243,7 @@
         <v>30</v>
       </c>
       <c r="C11">
-        <v>2799</v>
+        <v>2769</v>
       </c>
       <c r="D11" t="s">
         <v>31</v>
@@ -1257,7 +1257,7 @@
         <v>30</v>
       </c>
       <c r="C12">
-        <v>2232</v>
+        <v>2234</v>
       </c>
       <c r="D12" t="s">
         <v>31</v>
@@ -1271,7 +1271,7 @@
         <v>30</v>
       </c>
       <c r="C13">
-        <v>2223</v>
+        <v>2240</v>
       </c>
       <c r="D13" t="s">
         <v>31</v>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#28</t>
+    <t>#29</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 14:40:16 UTC</t>
+    <t>2026-06-22 15:04:31 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -69,6 +69,15 @@
   </si>
   <si>
     <t>📱 Android Mobile E2E</t>
+  </si>
+  <si>
+    <t>⚙️ Backend Service Tests</t>
+  </si>
+  <si>
+    <t>99.8%</t>
+  </si>
+  <si>
+    <t>FAIL</t>
   </si>
   <si>
     <t>🛡️ Backend Security Scan</t>
@@ -294,7 +303,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -319,8 +328,12 @@
       <b/>
       <color rgb="047857"/>
     </font>
+    <font>
+      <b/>
+      <color rgb="B91C1C"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -340,6 +353,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="D1FAE5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -362,7 +380,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -371,6 +389,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -711,7 +730,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G12"/>
+  <dimension ref="A1:G13"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="7" width="46" customWidth="1"/>
@@ -782,10 +801,10 @@
         <v>14</v>
       </c>
       <c r="B8">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C8">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -805,10 +824,10 @@
         <v>17</v>
       </c>
       <c r="B9">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="C9">
-        <v>300</v>
+        <v>400</v>
       </c>
       <c r="D9">
         <v>0</v>
@@ -828,68 +847,91 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>300</v>
-      </c>
-      <c r="C10" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C10">
+        <v>1198</v>
+      </c>
+      <c r="D10">
+        <v>2</v>
+      </c>
+      <c r="E10">
+        <v>0</v>
+      </c>
+      <c r="F10" t="s">
         <v>19</v>
       </c>
-      <c r="D10" t="s">
-        <v>19</v>
-      </c>
-      <c r="E10" t="s">
-        <v>19</v>
-      </c>
-      <c r="F10" t="s">
+      <c r="G10" s="6" t="s">
         <v>20</v>
-      </c>
-      <c r="G10" s="5" t="s">
-        <v>21</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11">
+        <v>400</v>
+      </c>
+      <c r="C11" t="s">
         <v>22</v>
       </c>
-      <c r="B11">
-        <v>6</v>
-      </c>
-      <c r="C11">
-        <v>6</v>
-      </c>
-      <c r="D11">
-        <v>0</v>
-      </c>
-      <c r="E11">
-        <v>0</v>
+      <c r="D11" t="s">
+        <v>22</v>
+      </c>
+      <c r="E11" t="s">
+        <v>22</v>
       </c>
       <c r="F11" t="s">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="G11" s="5" t="s">
-        <v>16</v>
+        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B12">
+        <v>6</v>
+      </c>
+      <c r="C12">
+        <v>6</v>
+      </c>
+      <c r="D12">
+        <v>0</v>
+      </c>
+      <c r="E12">
+        <v>0</v>
+      </c>
+      <c r="F12" t="s">
+        <v>15</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B13">
         <v>5824</v>
       </c>
-      <c r="C12" t="s">
-        <v>19</v>
-      </c>
-      <c r="D12" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" t="s">
-        <v>19</v>
-      </c>
-      <c r="F12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>25</v>
+      <c r="C13" t="s">
+        <v>22</v>
+      </c>
+      <c r="D13" t="s">
+        <v>22</v>
+      </c>
+      <c r="E13" t="s">
+        <v>22</v>
+      </c>
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="5" t="s">
+        <v>28</v>
       </c>
     </row>
   </sheetData>
@@ -912,171 +954,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>28</v>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>508</v>
+        <v>534</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>1177</v>
+        <v>1630</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4">
-        <v>3249</v>
+        <v>5255</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>985</v>
+        <v>903</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6">
-        <v>941</v>
+        <v>830</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>1819</v>
+        <v>1511</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>7341</v>
+        <v>6948</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>2498</v>
+        <v>2466</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>554</v>
+        <v>723</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11">
-        <v>173</v>
+        <v>230</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>9506</v>
+        <v>9270</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1096,185 +1138,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>26</v>
-      </c>
-      <c r="B1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="B1" s="7" t="s">
         <v>13</v>
       </c>
-      <c r="C1" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="D1" s="6" t="s">
-        <v>28</v>
+      <c r="C1" s="7" t="s">
+        <v>30</v>
+      </c>
+      <c r="D1" s="7" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B2" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C2">
-        <v>5218</v>
+        <v>5226</v>
       </c>
       <c r="D2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="B3" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C3">
-        <v>7815</v>
+        <v>7692</v>
       </c>
       <c r="D3" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="B4" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C4">
-        <v>18802</v>
+        <v>19308</v>
       </c>
       <c r="D4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C5">
-        <v>31011</v>
+        <v>30102</v>
       </c>
       <c r="D5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C6">
-        <v>14331</v>
+        <v>14294</v>
       </c>
       <c r="D6" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="B7" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C7">
-        <v>16471</v>
+        <v>16490</v>
       </c>
       <c r="D7" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>48</v>
+        <v>51</v>
       </c>
       <c r="B8" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C8">
-        <v>52148</v>
+        <v>55169</v>
       </c>
       <c r="D8" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>49</v>
+        <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C9">
-        <v>21398</v>
+        <v>21395</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>50</v>
+        <v>53</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C10">
-        <v>3047</v>
+        <v>2851</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="B11" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C11">
-        <v>2769</v>
+        <v>2750</v>
       </c>
       <c r="D11" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="B12" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C12">
-        <v>2234</v>
+        <v>2231</v>
       </c>
       <c r="D12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="C13">
-        <v>2240</v>
+        <v>2199</v>
       </c>
       <c r="D13" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
   </sheetData>
@@ -1295,109 +1337,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>54</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>55</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D1" s="6" t="s">
+      <c r="A1" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D1" s="7" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B2" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B3" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B4" t="s">
-        <v>61</v>
+        <v>64</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>62</v>
+        <v>65</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B5" t="s">
-        <v>63</v>
+        <v>66</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>64</v>
+        <v>67</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D6" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="B7" t="s">
-        <v>68</v>
+        <v>71</v>
       </c>
       <c r="C7" t="s">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B8" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1408,30 +1450,30 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>74</v>
       </c>
       <c r="C9">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>69</v>
+        <v>72</v>
       </c>
       <c r="B10" t="s">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
   </sheetData>
@@ -1451,91 +1493,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="6" t="s">
-        <v>73</v>
-      </c>
-      <c r="B1" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="C1" s="6" t="s">
-        <v>74</v>
+      <c r="A1" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="C1" s="7" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>75</v>
+        <v>78</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="B3" t="s">
-        <v>78</v>
+        <v>81</v>
       </c>
       <c r="C3" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="B4" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>83</v>
+        <v>86</v>
       </c>
       <c r="C5" t="s">
-        <v>84</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="B6" t="s">
-        <v>86</v>
+        <v>89</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>TrackBack Unified CI/CD Executive Dashboard</t>
   </si>
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#29</t>
+    <t>#30</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 15:04:31 UTC</t>
+    <t>2026-06-22 17:12:57 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -72,12 +72,6 @@
   </si>
   <si>
     <t>⚙️ Backend Service Tests</t>
-  </si>
-  <si>
-    <t>99.8%</t>
-  </si>
-  <si>
-    <t>FAIL</t>
   </si>
   <si>
     <t>🛡️ Backend Security Scan</t>
@@ -303,7 +297,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <color theme="1"/>
       <family val="2"/>
@@ -328,12 +322,8 @@
       <b/>
       <color rgb="047857"/>
     </font>
-    <font>
-      <b/>
-      <color rgb="B91C1C"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -353,11 +343,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="D1FAE5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FEE2E2"/>
       </patternFill>
     </fill>
   </fills>
@@ -380,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -389,7 +374,6 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -847,50 +831,50 @@
         <v>18</v>
       </c>
       <c r="B10">
-        <v>1200</v>
+        <v>400</v>
       </c>
       <c r="C10">
-        <v>1198</v>
+        <v>400</v>
       </c>
       <c r="D10">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E10">
         <v>0</v>
       </c>
       <c r="F10" t="s">
-        <v>19</v>
-      </c>
-      <c r="G10" s="6" t="s">
-        <v>20</v>
+        <v>15</v>
+      </c>
+      <c r="G10" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B11">
         <v>400</v>
       </c>
       <c r="C11" t="s">
+        <v>20</v>
+      </c>
+      <c r="D11" t="s">
+        <v>20</v>
+      </c>
+      <c r="E11" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" t="s">
+        <v>21</v>
+      </c>
+      <c r="G11" s="5" t="s">
         <v>22</v>
-      </c>
-      <c r="D11" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" t="s">
-        <v>22</v>
-      </c>
-      <c r="F11" t="s">
-        <v>23</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>24</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -913,25 +897,25 @@
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B13">
         <v>5824</v>
       </c>
       <c r="C13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="E13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F13" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G13" s="5" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
   </sheetData>
@@ -954,171 +938,171 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2">
-        <v>534</v>
+        <v>863</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>1630</v>
+        <v>1433</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>5255</v>
+        <v>4657</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>903</v>
+        <v>1192</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6">
-        <v>830</v>
+        <v>1023</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>1511</v>
+        <v>1193</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8">
-        <v>6948</v>
+        <v>6870</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>2466</v>
+        <v>2723</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10">
-        <v>723</v>
+        <v>709</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>9270</v>
+        <v>8898</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1138,185 +1122,185 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>28</v>
+      </c>
+      <c r="D1" s="6" t="s">
         <v>29</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>30</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B2" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C2">
-        <v>5226</v>
+        <v>5261</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C3">
-        <v>7692</v>
+        <v>8177</v>
       </c>
       <c r="D3" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B4" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4">
-        <v>19308</v>
+        <v>19462</v>
       </c>
       <c r="D4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B5" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C5">
-        <v>30102</v>
+        <v>30526</v>
       </c>
       <c r="D5" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C6">
-        <v>14294</v>
+        <v>14395</v>
       </c>
       <c r="D6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C7">
-        <v>16490</v>
+        <v>16474</v>
       </c>
       <c r="D7" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B8" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8">
-        <v>55169</v>
+        <v>52569</v>
       </c>
       <c r="D8" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B9" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C9">
-        <v>21395</v>
+        <v>21661</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B10" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C10">
-        <v>2851</v>
+        <v>3026</v>
       </c>
       <c r="D10" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="B11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C11">
-        <v>2750</v>
+        <v>2759</v>
       </c>
       <c r="D11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B12" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12">
-        <v>2231</v>
+        <v>2242</v>
       </c>
       <c r="D12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B13" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C13">
-        <v>2199</v>
+        <v>2285</v>
       </c>
       <c r="D13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
   </sheetData>
@@ -1337,109 +1321,109 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="6" t="s">
+        <v>55</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="C1" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="B1" s="7" t="s">
-        <v>58</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="6" t="s">
         <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="C2">
         <v>0</v>
       </c>
       <c r="D2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B3" t="s">
         <v>60</v>
-      </c>
-      <c r="B3" t="s">
-        <v>62</v>
       </c>
       <c r="C3">
         <v>3</v>
       </c>
       <c r="D3" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B4" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C4">
         <v>5</v>
       </c>
       <c r="D4" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C5">
         <v>3</v>
       </c>
       <c r="D5" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>66</v>
+      </c>
+      <c r="B6" t="s">
+        <v>67</v>
+      </c>
+      <c r="C6" t="s">
         <v>68</v>
       </c>
-      <c r="B6" t="s">
-        <v>69</v>
-      </c>
-      <c r="C6" t="s">
-        <v>70</v>
-      </c>
       <c r="D6" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B7" t="s">
+        <v>69</v>
+      </c>
+      <c r="C7" t="s">
         <v>68</v>
       </c>
-      <c r="B7" t="s">
-        <v>71</v>
-      </c>
-      <c r="C7" t="s">
-        <v>70</v>
-      </c>
       <c r="D7" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C8">
         <v>6</v>
@@ -1450,30 +1434,30 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" t="s">
         <v>72</v>
-      </c>
-      <c r="B9" t="s">
-        <v>74</v>
       </c>
       <c r="C9">
         <v>6</v>
       </c>
       <c r="D9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B10" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="C10">
         <v>0</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
   </sheetData>
@@ -1493,91 +1477,91 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>59</v>
-      </c>
-      <c r="C1" s="7" t="s">
-        <v>77</v>
+      <c r="A1" s="6" t="s">
+        <v>74</v>
+      </c>
+      <c r="B1" s="6" t="s">
+        <v>57</v>
+      </c>
+      <c r="C1" s="6" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B2">
         <v>97.07</v>
       </c>
       <c r="C2" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B3" t="s">
+        <v>79</v>
+      </c>
+      <c r="C3" t="s">
         <v>80</v>
-      </c>
-      <c r="B3" t="s">
-        <v>81</v>
-      </c>
-      <c r="C3" t="s">
-        <v>82</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="C4" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>83</v>
+      </c>
+      <c r="B5" t="s">
+        <v>84</v>
+      </c>
+      <c r="C5" t="s">
         <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B6" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B8">
         <v>5824</v>
       </c>
       <c r="C8" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/unified-summary.xlsx
+++ b/unified-summary.xlsx
@@ -23,13 +23,13 @@
     <t>Build Number:</t>
   </si>
   <si>
-    <t>#30</t>
+    <t>#31</t>
   </si>
   <si>
     <t>Execution Date:</t>
   </si>
   <si>
-    <t>2026-06-22 17:12:57 UTC</t>
+    <t>2026-06-23 08:07:26 UTC</t>
   </si>
   <si>
     <t>Branch:</t>
@@ -959,7 +959,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>863</v>
+        <v>880</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -973,7 +973,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>1433</v>
+        <v>1212</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -987,7 +987,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>4657</v>
+        <v>3625</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1001,7 +1001,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>1192</v>
+        <v>1164</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -1015,7 +1015,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>1023</v>
+        <v>1077</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1029,7 +1029,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>1193</v>
+        <v>1873</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -1043,7 +1043,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>6870</v>
+        <v>7054</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -1057,7 +1057,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>2723</v>
+        <v>2757</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -1071,7 +1071,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>709</v>
+        <v>726</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -1099,7 +1099,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>8898</v>
+        <v>8548</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -1143,7 +1143,7 @@
         <v>31</v>
       </c>
       <c r="C2">
-        <v>5261</v>
+        <v>5252</v>
       </c>
       <c r="D2" t="s">
         <v>32</v>
@@ -1157,7 +1157,7 @@
         <v>31</v>
       </c>
       <c r="C3">
-        <v>8177</v>
+        <v>7812</v>
       </c>
       <c r="D3" t="s">
         <v>32</v>
@@ -1171,7 +1171,7 @@
         <v>31</v>
       </c>
       <c r="C4">
-        <v>19462</v>
+        <v>19659</v>
       </c>
       <c r="D4" t="s">
         <v>32</v>
@@ -1185,7 +1185,7 @@
         <v>31</v>
       </c>
       <c r="C5">
-        <v>30526</v>
+        <v>30564</v>
       </c>
       <c r="D5" t="s">
         <v>32</v>
@@ -1199,7 +1199,7 @@
         <v>31</v>
       </c>
       <c r="C6">
-        <v>14395</v>
+        <v>14343</v>
       </c>
       <c r="D6" t="s">
         <v>32</v>
@@ -1213,7 +1213,7 @@
         <v>31</v>
       </c>
       <c r="C7">
-        <v>16474</v>
+        <v>16492</v>
       </c>
       <c r="D7" t="s">
         <v>32</v>
@@ -1227,7 +1227,7 @@
         <v>31</v>
       </c>
       <c r="C8">
-        <v>52569</v>
+        <v>52455</v>
       </c>
       <c r="D8" t="s">
         <v>32</v>
@@ -1241,7 +1241,7 @@
         <v>31</v>
       </c>
       <c r="C9">
-        <v>21661</v>
+        <v>21523</v>
       </c>
       <c r="D9" t="s">
         <v>32</v>
@@ -1255,7 +1255,7 @@
         <v>31</v>
       </c>
       <c r="C10">
-        <v>3026</v>
+        <v>2973</v>
       </c>
       <c r="D10" t="s">
         <v>32</v>
@@ -1269,7 +1269,7 @@
         <v>31</v>
       </c>
       <c r="C11">
-        <v>2759</v>
+        <v>2734</v>
       </c>
       <c r="D11" t="s">
         <v>32</v>
@@ -1283,7 +1283,7 @@
         <v>31</v>
       </c>
       <c r="C12">
-        <v>2242</v>
+        <v>2216</v>
       </c>
       <c r="D12" t="s">
         <v>32</v>
@@ -1297,7 +1297,7 @@
         <v>31</v>
       </c>
       <c r="C13">
-        <v>2285</v>
+        <v>2301</v>
       </c>
       <c r="D13" t="s">
         <v>32</v>
